--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="832">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T06:32:59+00:00</t>
+    <t>2026-09-05T07:29:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -661,6 +661,9 @@
   </si>
   <si>
     <t>10016766</t>
+  </si>
+  <si>
+    <t>10016778</t>
   </si>
   <si>
     <t>10016791</t>
@@ -2815,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D790"/>
+  <dimension ref="A1:D791"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10722,6 +10725,16 @@
       <c r="C790" s="2"/>
       <c r="D790" s="2"/>
     </row>
+    <row r="791">
+      <c r="A791" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B791" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C791" s="2"/>
+      <c r="D791" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-05T07:29:05+00:00</t>
+    <t>2026-09-07T08:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:59:25+00:00</t>
+    <t>2026-09-08T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:16:16+00:00</t>
+    <t>2026-09-09T11:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:12:15+00:00</t>
+    <t>2026-09-09T13:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-meddra.xlsx
+++ b/branches/dev/CodeSystem-meddra.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:30:31+00:00</t>
+    <t>2026-09-09T15:05:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
